--- a/ottoneu_power_rankings.xlsx
+++ b/ottoneu_power_rankings.xlsx
@@ -613,13 +613,13 @@
         <v>5314.6</v>
       </c>
       <c r="E2" t="n">
-        <v>2167.5</v>
+        <v>2363</v>
       </c>
       <c r="F2" t="n">
-        <v>7482.1</v>
+        <v>7677.6</v>
       </c>
       <c r="G2" t="n">
-        <v>17119.2</v>
+        <v>17314.7</v>
       </c>
       <c r="H2" t="n">
         <v>6422.2</v>
@@ -646,34 +646,34 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1544.2</v>
+        <v>1581.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>82.8</v>
+        <v>85</v>
       </c>
       <c r="R2" t="n">
-        <v>43.3</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
-        <v>1545.3</v>
+        <v>1586.2</v>
       </c>
       <c r="T2" t="n">
-        <v>491.1</v>
+        <v>503.8</v>
       </c>
       <c r="U2" t="n">
-        <v>174.7</v>
+        <v>180.2</v>
       </c>
       <c r="V2" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="W2" t="n">
         <v>1194.2</v>
       </c>
       <c r="X2" t="n">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="Y2" t="n">
-        <v>1544.2</v>
+        <v>1581.2</v>
       </c>
       <c r="Z2" t="n">
         <v>14692.1</v>
@@ -712,107 +712,107 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8817.299999999999</v>
+        <v>8960.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5864.6</v>
+        <v>5512.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2309.9</v>
+        <v>2708.6</v>
       </c>
       <c r="F3" t="n">
-        <v>8174.5</v>
+        <v>8221.4</v>
       </c>
       <c r="G3" t="n">
-        <v>16991.8</v>
+        <v>17181.9</v>
       </c>
       <c r="H3" t="n">
-        <v>6427.5</v>
+        <v>6189.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1650.7</v>
+        <v>1621.2</v>
       </c>
       <c r="J3" t="n">
-        <v>329.6</v>
+        <v>322.3</v>
       </c>
       <c r="K3" t="n">
-        <v>615.6</v>
+        <v>739.5</v>
       </c>
       <c r="L3" t="n">
-        <v>271.9</v>
+        <v>266.9</v>
       </c>
       <c r="M3" t="n">
-        <v>134.8</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>0.334</v>
+        <v>0.344</v>
       </c>
       <c r="O3" t="n">
-        <v>0.773</v>
+        <v>0.797</v>
       </c>
       <c r="P3" t="n">
-        <v>1594.1</v>
+        <v>1612.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>89</v>
+        <v>101.2</v>
       </c>
       <c r="R3" t="n">
-        <v>26.9</v>
+        <v>52.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1651.1</v>
+        <v>1686.7</v>
       </c>
       <c r="T3" t="n">
-        <v>449.3</v>
+        <v>496.9</v>
       </c>
       <c r="U3" t="n">
-        <v>166</v>
+        <v>173.6</v>
       </c>
       <c r="V3" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1244.1</v>
+        <v>1212.1</v>
       </c>
       <c r="X3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>1594.1</v>
+        <v>1612.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>11789.5</v>
+        <v>13545.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>10748</v>
+        <v>9550</v>
       </c>
       <c r="AB3" t="n">
-        <v>22537.5</v>
+        <v>23095.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AF3" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="AG3" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="AH3" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="4">
@@ -821,107 +821,107 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8960.5</v>
+        <v>8817.299999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>5512.8</v>
+        <v>5864.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2420.6</v>
+        <v>2334</v>
       </c>
       <c r="F4" t="n">
-        <v>7933.4</v>
+        <v>8198.6</v>
       </c>
       <c r="G4" t="n">
-        <v>16893.9</v>
+        <v>17015.9</v>
       </c>
       <c r="H4" t="n">
-        <v>6189.2</v>
+        <v>6427.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1621.2</v>
+        <v>1650.7</v>
       </c>
       <c r="J4" t="n">
-        <v>322.3</v>
+        <v>329.6</v>
       </c>
       <c r="K4" t="n">
-        <v>739.5</v>
+        <v>615.6</v>
       </c>
       <c r="L4" t="n">
-        <v>266.9</v>
+        <v>271.9</v>
       </c>
       <c r="M4" t="n">
-        <v>63</v>
+        <v>134.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.344</v>
+        <v>0.334</v>
       </c>
       <c r="O4" t="n">
-        <v>0.797</v>
+        <v>0.773</v>
       </c>
       <c r="P4" t="n">
-        <v>1562.1</v>
+        <v>1600.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>99.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="R4" t="n">
-        <v>40.1</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
-        <v>1639.1</v>
+        <v>1656</v>
       </c>
       <c r="T4" t="n">
-        <v>479.4</v>
+        <v>450.7</v>
       </c>
       <c r="U4" t="n">
-        <v>169.5</v>
+        <v>166.9</v>
       </c>
       <c r="V4" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1212.1</v>
+        <v>1244.1</v>
       </c>
       <c r="X4" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="Y4" t="n">
-        <v>1562.1</v>
+        <v>1600.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>13545.7</v>
+        <v>11789.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>9550</v>
+        <v>10748</v>
       </c>
       <c r="AB4" t="n">
-        <v>23095.7</v>
+        <v>22537.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AF4" t="n">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="AG4" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="AH4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AI4" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="5">
@@ -940,13 +940,13 @@
         <v>5564.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2088.5</v>
+        <v>2112</v>
       </c>
       <c r="F5" t="n">
-        <v>7653</v>
+        <v>7676.5</v>
       </c>
       <c r="G5" t="n">
-        <v>16824.2</v>
+        <v>16847.7</v>
       </c>
       <c r="H5" t="n">
         <v>6273.1</v>
@@ -973,34 +973,34 @@
         <v>0.798</v>
       </c>
       <c r="P5" t="n">
-        <v>1566.4</v>
+        <v>1573.4</v>
       </c>
       <c r="Q5" t="n">
         <v>56</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1639</v>
+        <v>1644.8</v>
       </c>
       <c r="T5" t="n">
-        <v>498.8</v>
+        <v>501.9</v>
       </c>
       <c r="U5" t="n">
-        <v>172.7</v>
+        <v>173.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="W5" t="n">
         <v>1216.4</v>
       </c>
       <c r="X5" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="Y5" t="n">
-        <v>1566.4</v>
+        <v>1573.4</v>
       </c>
       <c r="Z5" t="n">
         <v>12051.5</v>
@@ -1376,13 +1376,13 @@
         <v>4764</v>
       </c>
       <c r="E9" t="n">
-        <v>2437.6</v>
+        <v>2692.2</v>
       </c>
       <c r="F9" t="n">
-        <v>7201.6</v>
+        <v>7456.2</v>
       </c>
       <c r="G9" t="n">
-        <v>15110.1</v>
+        <v>15364.7</v>
       </c>
       <c r="H9" t="n">
         <v>5920.5</v>
@@ -1409,34 +1409,34 @@
         <v>0.764</v>
       </c>
       <c r="P9" t="n">
-        <v>1478</v>
+        <v>1528</v>
       </c>
       <c r="Q9" t="n">
-        <v>114.2</v>
+        <v>118</v>
       </c>
       <c r="R9" t="n">
-        <v>30.6</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
-        <v>1554.3</v>
+        <v>1612</v>
       </c>
       <c r="T9" t="n">
-        <v>560.8</v>
+        <v>583.3</v>
       </c>
       <c r="U9" t="n">
-        <v>163.1</v>
+        <v>170.2</v>
       </c>
       <c r="V9" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="W9" t="n">
         <v>1128</v>
       </c>
       <c r="X9" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>1478</v>
+        <v>1528</v>
       </c>
       <c r="Z9" t="n">
         <v>10103.9</v>
@@ -1485,13 +1485,13 @@
         <v>4837.5</v>
       </c>
       <c r="E10" t="n">
-        <v>2197.6</v>
+        <v>2436.9</v>
       </c>
       <c r="F10" t="n">
-        <v>7035.1</v>
+        <v>7274.4</v>
       </c>
       <c r="G10" t="n">
-        <v>15091</v>
+        <v>15330.3</v>
       </c>
       <c r="H10" t="n">
         <v>5899.8</v>
@@ -1518,22 +1518,22 @@
         <v>0.774</v>
       </c>
       <c r="P10" t="n">
-        <v>1495.8</v>
+        <v>1545.8</v>
       </c>
       <c r="Q10" t="n">
         <v>92</v>
       </c>
       <c r="R10" t="n">
-        <v>47</v>
+        <v>53.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1556.2</v>
+        <v>1606</v>
       </c>
       <c r="T10" t="n">
-        <v>526.5</v>
+        <v>546.4</v>
       </c>
       <c r="U10" t="n">
-        <v>181.9</v>
+        <v>187.3</v>
       </c>
       <c r="V10" t="n">
         <v>3.88</v>
@@ -1542,10 +1542,10 @@
         <v>1145.8</v>
       </c>
       <c r="X10" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>1495.8</v>
+        <v>1545.8</v>
       </c>
       <c r="Z10" t="n">
         <v>11436.7</v>
@@ -1584,107 +1584,107 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7602.3</v>
+        <v>8663.799999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>5112</v>
+        <v>4306</v>
       </c>
       <c r="E11" t="n">
-        <v>2119.9</v>
+        <v>2078.4</v>
       </c>
       <c r="F11" t="n">
-        <v>7231.9</v>
+        <v>6384.4</v>
       </c>
       <c r="G11" t="n">
-        <v>14834.2</v>
+        <v>15048.2</v>
       </c>
       <c r="H11" t="n">
-        <v>5700.3</v>
+        <v>6356.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1410.7</v>
+        <v>1651.1</v>
       </c>
       <c r="J11" t="n">
-        <v>269.5</v>
+        <v>315.7</v>
       </c>
       <c r="K11" t="n">
-        <v>621</v>
+        <v>668.6</v>
       </c>
       <c r="L11" t="n">
-        <v>222.6</v>
+        <v>235</v>
       </c>
       <c r="M11" t="n">
-        <v>184</v>
+        <v>164.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.754</v>
+        <v>0.767</v>
       </c>
       <c r="P11" t="n">
-        <v>1536</v>
+        <v>1431</v>
       </c>
       <c r="Q11" t="n">
-        <v>48</v>
+        <v>5.9</v>
       </c>
       <c r="R11" t="n">
-        <v>58.1</v>
+        <v>80</v>
       </c>
       <c r="S11" t="n">
-        <v>1577.4</v>
+        <v>1285.3</v>
       </c>
       <c r="T11" t="n">
-        <v>542.2</v>
+        <v>443.4</v>
       </c>
       <c r="U11" t="n">
-        <v>174.4</v>
+        <v>169.4</v>
       </c>
       <c r="V11" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="W11" t="n">
-        <v>1186</v>
+        <v>1031</v>
       </c>
       <c r="X11" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Y11" t="n">
-        <v>1536</v>
+        <v>1431</v>
       </c>
       <c r="Z11" t="n">
-        <v>7744.6</v>
+        <v>9652.200000000001</v>
       </c>
       <c r="AA11" t="n">
-        <v>7526</v>
+        <v>6851</v>
       </c>
       <c r="AB11" t="n">
-        <v>15270.6</v>
+        <v>16503.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="AF11" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="AG11" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="12">
@@ -1693,107 +1693,107 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8663.799999999999</v>
+        <v>7602.3</v>
       </c>
       <c r="D12" t="n">
-        <v>4306</v>
+        <v>5112</v>
       </c>
       <c r="E12" t="n">
-        <v>1832.3</v>
+        <v>2319.2</v>
       </c>
       <c r="F12" t="n">
-        <v>6138.3</v>
+        <v>7431.2</v>
       </c>
       <c r="G12" t="n">
-        <v>14802.1</v>
+        <v>15033.5</v>
       </c>
       <c r="H12" t="n">
-        <v>6356.3</v>
+        <v>5700.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1651.1</v>
+        <v>1410.7</v>
       </c>
       <c r="J12" t="n">
-        <v>315.7</v>
+        <v>269.5</v>
       </c>
       <c r="K12" t="n">
-        <v>668.6</v>
+        <v>621</v>
       </c>
       <c r="L12" t="n">
-        <v>235</v>
+        <v>222.6</v>
       </c>
       <c r="M12" t="n">
-        <v>164.6</v>
+        <v>184</v>
       </c>
       <c r="N12" t="n">
-        <v>0.333</v>
+        <v>0.327</v>
       </c>
       <c r="O12" t="n">
-        <v>0.767</v>
+        <v>0.754</v>
       </c>
       <c r="P12" t="n">
-        <v>1381</v>
+        <v>1586</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>48</v>
       </c>
       <c r="R12" t="n">
-        <v>70.3</v>
+        <v>58.8</v>
       </c>
       <c r="S12" t="n">
-        <v>1238.6</v>
+        <v>1632.9</v>
       </c>
       <c r="T12" t="n">
-        <v>427.9</v>
+        <v>570.4</v>
       </c>
       <c r="U12" t="n">
-        <v>162.9</v>
+        <v>179.9</v>
       </c>
       <c r="V12" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="W12" t="n">
-        <v>1031</v>
+        <v>1186</v>
       </c>
       <c r="X12" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Y12" t="n">
-        <v>1381</v>
+        <v>1586</v>
       </c>
       <c r="Z12" t="n">
-        <v>9652.200000000001</v>
+        <v>7744.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>6851</v>
+        <v>7526</v>
       </c>
       <c r="AB12" t="n">
-        <v>16503.2</v>
+        <v>15270.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="AF12" t="n">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="AG12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AI12" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="13">
@@ -2657,11 +2657,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>624413</v>
+        <v>687462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6.484076433</v>
+        <v>5.208695652</v>
       </c>
       <c r="H19" t="n">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="I19" t="n">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="J19" t="n">
-        <v>907.8</v>
+        <v>599</v>
       </c>
     </row>
     <row r="20">
@@ -2697,38 +2697,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>681082</v>
+        <v>700932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4.65</v>
+        <v>5.167826086</v>
       </c>
       <c r="H20" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="I20" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>651</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="21">
@@ -2737,38 +2737,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>663586</v>
+        <v>643446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5.523076923</v>
+        <v>5.329104477</v>
       </c>
       <c r="H21" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I21" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J21" t="n">
-        <v>773.2</v>
+        <v>714.1</v>
       </c>
     </row>
     <row r="22">
@@ -2777,38 +2777,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>663728</v>
+        <v>680977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5.499371069</v>
+        <v>4.854615384</v>
       </c>
       <c r="H22" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="I22" t="n">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>769.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="23">
@@ -2817,38 +2817,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>642715</v>
+        <v>571970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4.974522292</v>
+        <v>5.48</v>
       </c>
       <c r="H23" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="J23" t="n">
-        <v>84.59999999999999</v>
+        <v>575.4</v>
       </c>
     </row>
     <row r="24">
@@ -2857,38 +2857,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>596115</v>
+        <v>686948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.811688311</v>
+        <v>5.256923076</v>
       </c>
       <c r="H24" t="n">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I24" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J24" t="n">
-        <v>591.8</v>
+        <v>683.4</v>
       </c>
     </row>
     <row r="25">
@@ -2897,38 +2897,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>621439</v>
+        <v>682626</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5.818461538</v>
+        <v>4.591964285</v>
       </c>
       <c r="H25" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="I25" t="n">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>756.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="26">
@@ -2937,38 +2937,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>671739</v>
+        <v>605141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5.233834586</v>
+        <v>5.849006622</v>
       </c>
       <c r="H26" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="I26" t="n">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>696.1</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="27">
@@ -2977,38 +2977,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>595777</v>
+        <v>666182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jurickson Profar</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5.028187919</v>
+        <v>5.305921052</v>
       </c>
       <c r="H27" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I27" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="J27" t="n">
-        <v>749.2</v>
+        <v>684.5</v>
       </c>
     </row>
     <row r="28">
@@ -3017,11 +3017,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>671289</v>
+        <v>670541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tyler Freeman</t>
+          <t>Yordan Alvarez</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4.820253164</v>
+        <v>6.726153846</v>
       </c>
       <c r="H28" t="n">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="I28" t="n">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="J28" t="n">
-        <v>380.8</v>
+        <v>874.4</v>
       </c>
     </row>
     <row r="29">
@@ -3057,11 +3057,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>808982</v>
+        <v>701350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Roman Anthony</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3079,16 +3079,16 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4.677304964</v>
+        <v>5.650684931</v>
       </c>
       <c r="H29" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I29" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J29" t="n">
-        <v>659.5</v>
+        <v>825</v>
       </c>
     </row>
     <row r="30">
@@ -3097,11 +3097,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>607043</v>
+        <v>545361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3119,16 +3119,16 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4.629452054</v>
+        <v>5.451538461</v>
       </c>
       <c r="H30" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="I30" t="n">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="J30" t="n">
-        <v>314.8</v>
+        <v>708.7</v>
       </c>
     </row>
     <row r="31">
@@ -3137,38 +3137,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>642715</v>
+        <v>641355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4.974522292</v>
+        <v>5.123776223</v>
       </c>
       <c r="H31" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="I31" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J31" t="n">
-        <v>696.4</v>
+        <v>732.7</v>
       </c>
     </row>
     <row r="32">
@@ -3177,38 +3177,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>624413</v>
+        <v>662139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pete Alonso</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6.484076433</v>
+        <v>4.981884057</v>
       </c>
       <c r="H32" t="n">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="J32" t="n">
-        <v>110.2</v>
+        <v>687.5</v>
       </c>
     </row>
     <row r="33">
@@ -3217,38 +3217,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>663586</v>
+        <v>663757</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5.523076923</v>
+        <v>4.975396825</v>
       </c>
       <c r="H33" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J33" t="n">
-        <v>88.40000000000001</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="34">
@@ -3257,38 +3257,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>663728</v>
+        <v>605141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5.499371069</v>
+        <v>5.849006622</v>
       </c>
       <c r="H34" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="J34" t="n">
-        <v>104.5</v>
+        <v>818.9</v>
       </c>
     </row>
     <row r="35">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>575929</v>
+        <v>666182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3310,30 +3310,30 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5.485106382</v>
+        <v>5.305921052</v>
       </c>
       <c r="H35" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I35" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>482.7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3341,39 +3341,39 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>687462</v>
+        <v>700932</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Util</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kyle Manzardo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Spencer Horwitz</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
       <c r="G36" t="n">
-        <v>5.208695652</v>
+        <v>5.167826086</v>
       </c>
       <c r="H36" t="n">
         <v>115</v>
       </c>
       <c r="I36" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="J36" t="n">
-        <v>599</v>
+        <v>465.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3381,34 +3381,34 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>700932</v>
+        <v>676475</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Util</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Alec Burleson</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Kyle Manzardo</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
       <c r="G37" t="n">
-        <v>5.167826086</v>
+        <v>5.05971223</v>
       </c>
       <c r="H37" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>129.2</v>
+        <v>136.6</v>
       </c>
     </row>
     <row r="38">
@@ -3417,38 +3417,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>643446</v>
+        <v>624413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5.329104477</v>
+        <v>6.484076433</v>
       </c>
       <c r="H38" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I38" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J38" t="n">
-        <v>714.1</v>
+        <v>907.8</v>
       </c>
     </row>
     <row r="39">
@@ -3457,11 +3457,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>680977</v>
+        <v>681082</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3479,16 +3479,16 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4.854615384</v>
+        <v>4.65</v>
       </c>
       <c r="H39" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="J39" t="n">
-        <v>29.1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="40">
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>571970</v>
+        <v>663586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5.48</v>
+        <v>5.523076923</v>
       </c>
       <c r="H40" t="n">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="I40" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="J40" t="n">
-        <v>575.4</v>
+        <v>773.2</v>
       </c>
     </row>
     <row r="41">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>686948</v>
+        <v>663728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5.256923076</v>
+        <v>5.499371069</v>
       </c>
       <c r="H41" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="I41" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J41" t="n">
-        <v>683.4</v>
+        <v>769.9</v>
       </c>
     </row>
     <row r="42">
@@ -3577,38 +3577,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>682626</v>
+        <v>642715</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4.591964285</v>
+        <v>4.974522292</v>
       </c>
       <c r="H42" t="n">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>45.9</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3617,11 +3617,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>605141</v>
+        <v>596115</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3639,16 +3639,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5.849006622</v>
+        <v>4.811688311</v>
       </c>
       <c r="H43" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="J43" t="n">
-        <v>64.3</v>
+        <v>591.8</v>
       </c>
     </row>
     <row r="44">
@@ -3657,38 +3657,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>666182</v>
+        <v>621439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Byron Buxton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>5.305921052</v>
+        <v>5.818461538</v>
       </c>
       <c r="H44" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="I44" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J44" t="n">
-        <v>684.5</v>
+        <v>756.4</v>
       </c>
     </row>
     <row r="45">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>670541</v>
+        <v>671739</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yordan Alvarez</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3719,16 +3719,16 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>6.726153846</v>
+        <v>5.233834586</v>
       </c>
       <c r="H45" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I45" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J45" t="n">
-        <v>874.4</v>
+        <v>696.1</v>
       </c>
     </row>
     <row r="46">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>701350</v>
+        <v>595777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Roman Anthony</t>
+          <t>Jurickson Profar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3759,16 +3759,16 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5.650684931</v>
+        <v>5.028187919</v>
       </c>
       <c r="H46" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I46" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J46" t="n">
-        <v>825</v>
+        <v>749.2</v>
       </c>
     </row>
     <row r="47">
@@ -3777,11 +3777,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>545361</v>
+        <v>671289</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Tyler Freeman</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5.451538461</v>
+        <v>4.820253164</v>
       </c>
       <c r="H47" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="I47" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="J47" t="n">
-        <v>708.7</v>
+        <v>380.8</v>
       </c>
     </row>
     <row r="48">
@@ -3817,11 +3817,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>641355</v>
+        <v>808982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3839,16 +3839,16 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>5.123776223</v>
+        <v>4.677304964</v>
       </c>
       <c r="H48" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I48" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J48" t="n">
-        <v>732.7</v>
+        <v>659.5</v>
       </c>
     </row>
     <row r="49">
@@ -3857,11 +3857,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>662139</v>
+        <v>607043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3879,16 +3879,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4.981884057</v>
+        <v>4.629452054</v>
       </c>
       <c r="H49" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I49" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="J49" t="n">
-        <v>687.5</v>
+        <v>314.8</v>
       </c>
     </row>
     <row r="50">
@@ -3897,38 +3897,38 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>663757</v>
+        <v>642715</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>4.975396825</v>
+        <v>4.974522292</v>
       </c>
       <c r="H50" t="n">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="I50" t="n">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="J50" t="n">
-        <v>64.7</v>
+        <v>696.4</v>
       </c>
     </row>
     <row r="51">
@@ -3937,38 +3937,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>605141</v>
+        <v>624413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Util</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Pete Alonso</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5.849006622</v>
+        <v>6.484076433</v>
       </c>
       <c r="H51" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I51" t="n">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>818.9</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="52">
@@ -3977,11 +3977,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>666182</v>
+        <v>663586</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3990,25 +3990,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>5.305921052</v>
+        <v>5.523076923</v>
       </c>
       <c r="H52" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>122</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4017,11 +4017,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>700932</v>
+        <v>663728</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4030,25 +4030,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5.167826086</v>
+        <v>5.499371069</v>
       </c>
       <c r="H53" t="n">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="I53" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>465.1</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="54">
@@ -4057,11 +4057,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>676475</v>
+        <v>575929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4079,16 +4079,16 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>5.05971223</v>
+        <v>5.485106382</v>
       </c>
       <c r="H54" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="J54" t="n">
-        <v>136.6</v>
+        <v>482.7</v>
       </c>
     </row>
     <row r="55">
@@ -8177,11 +8177,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>547180</v>
+        <v>691723</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8199,16 +8199,16 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>6.157792207</v>
+        <v>5.058823529</v>
       </c>
       <c r="H157" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="I157" t="n">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="J157" t="n">
-        <v>862.1</v>
+        <v>172</v>
       </c>
     </row>
     <row r="158">
@@ -8217,38 +8217,38 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>683953</v>
+        <v>694384</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>4.15090909</v>
+        <v>4.758741258</v>
       </c>
       <c r="H158" t="n">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="I158" t="n">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="J158" t="n">
-        <v>228.3</v>
+        <v>504.4</v>
       </c>
     </row>
     <row r="159">
@@ -8257,11 +8257,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>682668</v>
+        <v>690993</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8279,16 +8279,16 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>3.469565217</v>
+        <v>5.17699115</v>
       </c>
       <c r="H159" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I159" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="J159" t="n">
-        <v>294.9</v>
+        <v>585</v>
       </c>
     </row>
     <row r="160">
@@ -8297,38 +8297,38 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>691785</v>
+        <v>807712</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Marcelo Mayer</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>4.052173913</v>
+        <v>5.173076923</v>
       </c>
       <c r="H160" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="I160" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="J160" t="n">
-        <v>372.8</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="161">
@@ -8337,38 +8337,38 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>691019</v>
+        <v>691781</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>4.206956521</v>
+        <v>3.823809523</v>
       </c>
       <c r="H161" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I161" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J161" t="n">
-        <v>483.8</v>
+        <v>481.8</v>
       </c>
     </row>
     <row r="162">
@@ -8377,38 +8377,38 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>683002</v>
+        <v>694208</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>6.16025641</v>
+        <v>4.392592592</v>
       </c>
       <c r="H162" t="n">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="I162" t="n">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="J162" t="n">
-        <v>98.59999999999999</v>
+        <v>355.8</v>
       </c>
     </row>
     <row r="163">
@@ -8417,38 +8417,38 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>695657</v>
+        <v>693307</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>4.387050359</v>
+        <v>4.08090909</v>
       </c>
       <c r="H163" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="I163" t="n">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="J163" t="n">
-        <v>544</v>
+        <v>240.8</v>
       </c>
     </row>
     <row r="164">
@@ -8457,38 +8457,38 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>682998</v>
+        <v>677951</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>6.178767123</v>
+        <v>6.196815286</v>
       </c>
       <c r="H164" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I164" t="n">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="J164" t="n">
-        <v>902.1</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="165">
@@ -8497,38 +8497,38 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>665833</v>
+        <v>807712</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>5.4048</v>
+        <v>5.173076923</v>
       </c>
       <c r="H165" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I165" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="J165" t="n">
-        <v>675.6</v>
+        <v>532.8</v>
       </c>
     </row>
     <row r="166">
@@ -8537,38 +8537,38 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>592885</v>
+        <v>669236</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jeremiah Jackson</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>5.025342465</v>
+        <v>4.433333333</v>
       </c>
       <c r="H166" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="I166" t="n">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="J166" t="n">
-        <v>733.7</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="167">
@@ -8577,11 +8577,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>682987</v>
+        <v>665742</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Juan Soto</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8599,16 +8599,16 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>4.72</v>
+        <v>7.189308176</v>
       </c>
       <c r="H167" t="n">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="J167" t="n">
-        <v>23.6</v>
+        <v>1143.1</v>
       </c>
     </row>
     <row r="168">
@@ -8617,11 +8617,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>686611</v>
+        <v>665487</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8639,16 +8639,16 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>4.509420289</v>
+        <v>5.869871794</v>
       </c>
       <c r="H168" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I168" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="J168" t="n">
-        <v>622.3</v>
+        <v>915.7</v>
       </c>
     </row>
     <row r="169">
@@ -8657,11 +8657,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>695731</v>
+        <v>701538</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8679,16 +8679,16 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>4.221875</v>
+        <v>5.208904109</v>
       </c>
       <c r="H169" t="n">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="I169" t="n">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="J169" t="n">
-        <v>135.1</v>
+        <v>760.5</v>
       </c>
     </row>
     <row r="170">
@@ -8697,38 +8697,38 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>683002</v>
+        <v>687597</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>6.16025641</v>
+        <v>4.844776119</v>
       </c>
       <c r="H170" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I170" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J170" t="n">
-        <v>862.4</v>
+        <v>649.2</v>
       </c>
     </row>
     <row r="171">
@@ -8737,38 +8737,38 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>547180</v>
+        <v>805805</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>6.157792207</v>
+        <v>4.631578947</v>
       </c>
       <c r="H171" t="n">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="I171" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J171" t="n">
-        <v>86.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="172">
@@ -8777,43 +8777,43 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>700250</v>
+        <v>670770</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>5.37109375</v>
+        <v>4.444444444</v>
       </c>
       <c r="H172" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="I172" t="n">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="J172" t="n">
-        <v>676.8</v>
+        <v>382.2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -8821,39 +8821,39 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>691723</v>
+        <v>677951</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>5.058823529</v>
+        <v>6.196815286</v>
       </c>
       <c r="H173" t="n">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="I173" t="n">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="J173" t="n">
-        <v>172</v>
+        <v>867.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>Util</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8885,15 +8885,15 @@
         <v>143</v>
       </c>
       <c r="I174" t="n">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="J174" t="n">
-        <v>504.4</v>
+        <v>176.1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -8901,39 +8901,39 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>690993</v>
+        <v>805249</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Util</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Otto Kemp</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>5.17699115</v>
+        <v>4.63015873</v>
       </c>
       <c r="H175" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="I175" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="J175" t="n">
-        <v>585</v>
+        <v>291.7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -8941,34 +8941,34 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>807712</v>
+        <v>805811</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Util</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Bryce Eldridge</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>5.173076923</v>
+        <v>4.585576923</v>
       </c>
       <c r="H176" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I176" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J176" t="n">
-        <v>139.7</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="177">
@@ -8977,38 +8977,38 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>691781</v>
+        <v>547180</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>3.823809523</v>
+        <v>6.157792207</v>
       </c>
       <c r="H177" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I177" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J177" t="n">
-        <v>481.8</v>
+        <v>862.1</v>
       </c>
     </row>
     <row r="178">
@@ -9017,38 +9017,38 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>694208</v>
+        <v>683953</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>4.392592592</v>
+        <v>4.15090909</v>
       </c>
       <c r="H178" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="I178" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="J178" t="n">
-        <v>355.8</v>
+        <v>228.3</v>
       </c>
     </row>
     <row r="179">
@@ -9057,38 +9057,38 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>693307</v>
+        <v>682668</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>4.08090909</v>
+        <v>3.469565217</v>
       </c>
       <c r="H179" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="I179" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="J179" t="n">
-        <v>240.8</v>
+        <v>294.9</v>
       </c>
     </row>
     <row r="180">
@@ -9097,38 +9097,38 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>677951</v>
+        <v>691785</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Marcelo Mayer</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>6.196815286</v>
+        <v>4.052173913</v>
       </c>
       <c r="H180" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="I180" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="J180" t="n">
-        <v>105.3</v>
+        <v>372.8</v>
       </c>
     </row>
     <row r="181">
@@ -9137,38 +9137,38 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>807712</v>
+        <v>691019</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>MIF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>5.173076923</v>
+        <v>4.206956521</v>
       </c>
       <c r="H181" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I181" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J181" t="n">
-        <v>532.8</v>
+        <v>483.8</v>
       </c>
     </row>
     <row r="182">
@@ -9177,11 +9177,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>669236</v>
+        <v>683002</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -9190,25 +9190,25 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Jeremiah Jackson</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>4.433333333</v>
+        <v>6.16025641</v>
       </c>
       <c r="H182" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="I182" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J182" t="n">
-        <v>88.7</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -9217,38 +9217,38 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>665742</v>
+        <v>695657</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>MIF</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Juan Soto</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>7.189308176</v>
+        <v>4.387050359</v>
       </c>
       <c r="H183" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="I183" t="n">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="J183" t="n">
-        <v>1143.1</v>
+        <v>544</v>
       </c>
     </row>
     <row r="184">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>665487</v>
+        <v>682998</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -9279,16 +9279,16 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>5.869871794</v>
+        <v>6.178767123</v>
       </c>
       <c r="H184" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I184" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="J184" t="n">
-        <v>915.7</v>
+        <v>902.1</v>
       </c>
     </row>
     <row r="185">
@@ -9297,11 +9297,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>701538</v>
+        <v>665833</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -9319,16 +9319,16 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>5.208904109</v>
+        <v>5.4048</v>
       </c>
       <c r="H185" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="I185" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="J185" t="n">
-        <v>760.5</v>
+        <v>675.6</v>
       </c>
     </row>
     <row r="186">
@@ -9337,11 +9337,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>687597</v>
+        <v>592885</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -9359,16 +9359,16 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>4.844776119</v>
+        <v>5.025342465</v>
       </c>
       <c r="H186" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I186" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J186" t="n">
-        <v>649.2</v>
+        <v>733.7</v>
       </c>
     </row>
     <row r="187">
@@ -9377,11 +9377,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>805805</v>
+        <v>682987</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -9399,16 +9399,16 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>4.631578947</v>
+        <v>4.72</v>
       </c>
       <c r="H187" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I187" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J187" t="n">
-        <v>88</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="188">
@@ -9417,11 +9417,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>670770</v>
+        <v>686611</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9439,16 +9439,16 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>4.444444444</v>
+        <v>4.509420289</v>
       </c>
       <c r="H188" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I188" t="n">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="J188" t="n">
-        <v>382.2</v>
+        <v>622.3</v>
       </c>
     </row>
     <row r="189">
@@ -9457,38 +9457,38 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>677951</v>
+        <v>695731</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bobby Witt Jr.</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>OF</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>6.196815286</v>
+        <v>4.221875</v>
       </c>
       <c r="H189" t="n">
-        <v>157</v>
+        <v>32</v>
       </c>
       <c r="I189" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="J189" t="n">
-        <v>867.6</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="190">
@@ -9497,38 +9497,38 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>694384</v>
+        <v>683002</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Util</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>4.758741258</v>
+        <v>6.16025641</v>
       </c>
       <c r="H190" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="I190" t="n">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="J190" t="n">
-        <v>176.1</v>
+        <v>862.4</v>
       </c>
     </row>
     <row r="191">
@@ -9537,11 +9537,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>805249</v>
+        <v>547180</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Otto Kemp</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9559,16 +9559,16 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>4.63015873</v>
+        <v>6.157792207</v>
       </c>
       <c r="H191" t="n">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="I191" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J191" t="n">
-        <v>291.7</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="192">
@@ -9577,11 +9577,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>805811</v>
+        <v>700250</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bryce Eldridge</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9599,16 +9599,16 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>4.585576923</v>
+        <v>5.37109375</v>
       </c>
       <c r="H192" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="I192" t="n">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="J192" t="n">
-        <v>183.4</v>
+        <v>676.8</v>
       </c>
     </row>
     <row r="193">
@@ -10656,15 +10656,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>676979</v>
+        <v>657277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Garrett Crochet</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10679,16 +10679,16 @@
         <v>32</v>
       </c>
       <c r="H10" t="n">
-        <v>6.22</v>
+        <v>6.34</v>
       </c>
       <c r="I10" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J10" t="n">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="K10" t="n">
-        <v>1073</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="11">
@@ -10697,15 +10697,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>650911</v>
+        <v>676440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10714,22 +10714,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>6.22</v>
+        <v>5.84</v>
       </c>
       <c r="I11" t="n">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="J11" t="n">
-        <v>983</v>
+        <v>759</v>
       </c>
       <c r="K11" t="n">
-        <v>983</v>
+        <v>759</v>
       </c>
     </row>
     <row r="12">
@@ -10738,15 +10738,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>543243</v>
+        <v>554430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10755,22 +10755,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H12" t="n">
-        <v>5.68</v>
+        <v>6.12</v>
       </c>
       <c r="I12" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="J12" t="n">
-        <v>802</v>
+        <v>752</v>
       </c>
       <c r="K12" t="n">
-        <v>802</v>
+        <v>752</v>
       </c>
     </row>
     <row r="13">
@@ -10779,15 +10779,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>624133</v>
+        <v>669302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ranger Suárez</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10802,16 +10802,16 @@
         <v>29</v>
       </c>
       <c r="H13" t="n">
-        <v>5.72</v>
+        <v>5.52</v>
       </c>
       <c r="I13" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J13" t="n">
-        <v>769</v>
+        <v>745</v>
       </c>
       <c r="K13" t="n">
-        <v>769</v>
+        <v>745</v>
       </c>
     </row>
     <row r="14">
@@ -10820,15 +10820,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>594798</v>
+        <v>656849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10843,16 +10843,16 @@
         <v>29</v>
       </c>
       <c r="H14" t="n">
-        <v>5.59</v>
+        <v>5.41</v>
       </c>
       <c r="I14" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J14" t="n">
-        <v>747</v>
+        <v>679</v>
       </c>
       <c r="K14" t="n">
-        <v>747</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15">
@@ -10861,15 +10861,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>672282</v>
+        <v>642547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10878,22 +10878,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>5.88</v>
+        <v>5.38</v>
       </c>
       <c r="I15" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J15" t="n">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="K15" t="n">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16">
@@ -10902,15 +10902,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>607259</v>
+        <v>805673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10925,16 +10925,16 @@
         <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>7.19</v>
+        <v>5.67</v>
       </c>
       <c r="I16" t="n">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="J16" t="n">
-        <v>638</v>
+        <v>535</v>
       </c>
       <c r="K16" t="n">
-        <v>638</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17">
@@ -10943,15 +10943,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>691587</v>
+        <v>543135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10960,22 +10960,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>4.18</v>
+        <v>5.93</v>
       </c>
       <c r="I17" t="n">
-        <v>50.1</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>489</v>
+        <v>720</v>
       </c>
       <c r="K17" t="n">
-        <v>209.6</v>
+        <v>322.8</v>
       </c>
     </row>
     <row r="18">
@@ -10984,15 +10984,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>657277</v>
+        <v>676979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -11007,16 +11007,16 @@
         <v>32</v>
       </c>
       <c r="H18" t="n">
-        <v>6.34</v>
+        <v>6.22</v>
       </c>
       <c r="I18" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J18" t="n">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="K18" t="n">
-        <v>1060</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="19">
@@ -11025,15 +11025,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>676440</v>
+        <v>650911</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11042,22 +11042,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>5.84</v>
+        <v>6.22</v>
       </c>
       <c r="I19" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="J19" t="n">
-        <v>759</v>
+        <v>983</v>
       </c>
       <c r="K19" t="n">
-        <v>759</v>
+        <v>983</v>
       </c>
     </row>
     <row r="20">
@@ -11066,15 +11066,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>554430</v>
+        <v>543243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11083,22 +11083,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>6.12</v>
+        <v>5.68</v>
       </c>
       <c r="I20" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J20" t="n">
-        <v>752</v>
+        <v>802</v>
       </c>
       <c r="K20" t="n">
-        <v>752</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21">
@@ -11107,15 +11107,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>669302</v>
+        <v>624133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Ranger Suárez</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11130,16 +11130,16 @@
         <v>29</v>
       </c>
       <c r="H21" t="n">
-        <v>5.52</v>
+        <v>5.72</v>
       </c>
       <c r="I21" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J21" t="n">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="K21" t="n">
-        <v>745</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22">
@@ -11148,15 +11148,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>656849</v>
+        <v>594798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11171,16 +11171,16 @@
         <v>29</v>
       </c>
       <c r="H22" t="n">
-        <v>5.41</v>
+        <v>5.59</v>
       </c>
       <c r="I22" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J22" t="n">
-        <v>679</v>
+        <v>747</v>
       </c>
       <c r="K22" t="n">
-        <v>679</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23">
@@ -11189,15 +11189,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>642547</v>
+        <v>672282</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11206,22 +11206,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H23" t="n">
-        <v>5.38</v>
+        <v>5.88</v>
       </c>
       <c r="I23" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J23" t="n">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="K23" t="n">
-        <v>660</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24">
@@ -11230,15 +11230,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>805673</v>
+        <v>607259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11253,16 +11253,16 @@
         <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>5.67</v>
+        <v>7.19</v>
       </c>
       <c r="I24" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="J24" t="n">
-        <v>535</v>
+        <v>638</v>
       </c>
       <c r="K24" t="n">
-        <v>535</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25">
@@ -11271,15 +11271,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>543135</v>
+        <v>691587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11288,22 +11288,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>5.93</v>
+        <v>4.18</v>
       </c>
       <c r="I25" t="n">
-        <v>77.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="J25" t="n">
-        <v>720</v>
+        <v>489</v>
       </c>
       <c r="K25" t="n">
-        <v>322.8</v>
+        <v>209.6</v>
       </c>
     </row>
     <row r="26">
@@ -13444,15 +13444,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>664285</v>
+        <v>645261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Sandy Alcantara</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -13467,16 +13467,16 @@
         <v>31</v>
       </c>
       <c r="H78" t="n">
-        <v>6.45</v>
+        <v>6.1</v>
       </c>
       <c r="I78" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="J78" t="n">
-        <v>908</v>
+        <v>816</v>
       </c>
       <c r="K78" t="n">
-        <v>908</v>
+        <v>816</v>
       </c>
     </row>
     <row r="79">
@@ -13485,15 +13485,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>671096</v>
+        <v>808967</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -13502,22 +13502,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H79" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J79" t="n">
-        <v>693</v>
+        <v>758</v>
       </c>
       <c r="K79" t="n">
-        <v>693</v>
+        <v>758</v>
       </c>
     </row>
     <row r="80">
@@ -13526,15 +13526,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>607074</v>
+        <v>608379</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Carlos Rodón</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -13543,22 +13543,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H80" t="n">
-        <v>5.29</v>
+        <v>5.48</v>
       </c>
       <c r="I80" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J80" t="n">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="K80" t="n">
-        <v>626</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81">
@@ -13567,15 +13567,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>686218</v>
+        <v>605288</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -13584,22 +13584,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G81" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H81" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="I81" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J81" t="n">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="K81" t="n">
-        <v>589</v>
+        <v>574</v>
       </c>
     </row>
     <row r="82">
@@ -13608,15 +13608,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>694819</v>
+        <v>702070</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -13625,22 +13625,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H82" t="n">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="I82" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J82" t="n">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="K82" t="n">
-        <v>563</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83">
@@ -13649,15 +13649,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>696149</v>
+        <v>671737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -13666,22 +13666,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H83" t="n">
-        <v>5.12</v>
+        <v>5.65</v>
       </c>
       <c r="I83" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J83" t="n">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="K83" t="n">
-        <v>554</v>
+        <v>524</v>
       </c>
     </row>
     <row r="84">
@@ -13690,15 +13690,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>702056</v>
+        <v>673540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Kodai Senga</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -13707,27 +13707,27 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G84" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H84" t="n">
-        <v>4.79</v>
+        <v>6.05</v>
       </c>
       <c r="I84" t="n">
         <v>115</v>
       </c>
       <c r="J84" t="n">
-        <v>498</v>
+        <v>455</v>
       </c>
       <c r="K84" t="n">
-        <v>498</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -13735,11 +13735,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>701656</v>
+        <v>664285</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -13748,27 +13748,27 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G85" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H85" t="n">
-        <v>6.06</v>
+        <v>6.45</v>
       </c>
       <c r="I85" t="n">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="J85" t="n">
-        <v>393</v>
+        <v>908</v>
       </c>
       <c r="K85" t="n">
-        <v>393</v>
+        <v>908</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -13776,11 +13776,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>663568</v>
+        <v>671096</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -13789,22 +13789,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H86" t="n">
-        <v>8.75</v>
+        <v>5.55</v>
       </c>
       <c r="I86" t="n">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="J86" t="n">
-        <v>288</v>
+        <v>693</v>
       </c>
       <c r="K86" t="n">
-        <v>288</v>
+        <v>693</v>
       </c>
     </row>
     <row r="87">
@@ -13813,15 +13813,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>645261</v>
+        <v>607074</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Carlos Rodón</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13830,22 +13830,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G87" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H87" t="n">
-        <v>6.1</v>
+        <v>5.29</v>
       </c>
       <c r="I87" t="n">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="J87" t="n">
-        <v>816</v>
+        <v>626</v>
       </c>
       <c r="K87" t="n">
-        <v>816</v>
+        <v>626</v>
       </c>
     </row>
     <row r="88">
@@ -13854,15 +13854,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>808967</v>
+        <v>686218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -13871,22 +13871,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>5.58</v>
       </c>
       <c r="I88" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="J88" t="n">
-        <v>758</v>
+        <v>589</v>
       </c>
       <c r="K88" t="n">
-        <v>758</v>
+        <v>589</v>
       </c>
     </row>
     <row r="89">
@@ -13895,15 +13895,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>608379</v>
+        <v>694819</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -13912,22 +13912,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G89" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H89" t="n">
-        <v>5.48</v>
+        <v>5.33</v>
       </c>
       <c r="I89" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="J89" t="n">
-        <v>640</v>
+        <v>563</v>
       </c>
       <c r="K89" t="n">
-        <v>640</v>
+        <v>563</v>
       </c>
     </row>
     <row r="90">
@@ -13936,15 +13936,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>605288</v>
+        <v>696149</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13959,16 +13959,16 @@
         <v>26</v>
       </c>
       <c r="H90" t="n">
-        <v>5.62</v>
+        <v>5.12</v>
       </c>
       <c r="I90" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="J90" t="n">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="K90" t="n">
-        <v>574</v>
+        <v>554</v>
       </c>
     </row>
     <row r="91">
@@ -13977,15 +13977,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>702070</v>
+        <v>702056</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13994,22 +13994,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G91" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H91" t="n">
-        <v>5.23</v>
+        <v>4.79</v>
       </c>
       <c r="I91" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="J91" t="n">
-        <v>539</v>
+        <v>498</v>
       </c>
       <c r="K91" t="n">
-        <v>539</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92">
@@ -14018,15 +14018,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>671737</v>
+        <v>701656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -14035,22 +14035,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G92" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H92" t="n">
-        <v>5.65</v>
+        <v>6.06</v>
       </c>
       <c r="I92" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="J92" t="n">
-        <v>524</v>
+        <v>393</v>
       </c>
       <c r="K92" t="n">
-        <v>524</v>
+        <v>393</v>
       </c>
     </row>
     <row r="93">
@@ -14059,15 +14059,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>673540</v>
+        <v>663568</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Kodai Senga</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -14076,22 +14076,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H93" t="n">
-        <v>6.05</v>
+        <v>8.75</v>
       </c>
       <c r="I93" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="J93" t="n">
-        <v>455</v>
+        <v>288</v>
       </c>
       <c r="K93" t="n">
-        <v>455</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94">
@@ -14433,7 +14433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14718,11 +14718,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>642100</v>
+        <v>596133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gabe Speier</t>
+          <t>Luke Weaver</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -14731,31 +14731,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H6" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I6" t="n">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="J6" t="n">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -14768,11 +14768,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>596133</v>
+        <v>642100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Luke Weaver</t>
+          <t>Gabe Speier</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -14781,31 +14781,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="I7" t="n">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="J7" t="n">
-        <v>158.5</v>
+        <v>318</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -14814,15 +14814,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>661395</v>
+        <v>621242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jhoan Duran</t>
+          <t>Edwin Díaz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -14831,25 +14831,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I8" t="n">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="J8" t="n">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
@@ -14864,15 +14864,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>691799</v>
+        <v>547973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Grant Taylor</t>
+          <t>Aroldis Chapman</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -14881,31 +14881,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I9" t="n">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="J9" t="n">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -14914,15 +14914,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>662253</v>
+        <v>628452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Andrés Muñoz</t>
+          <t>Raisel Iglesias</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -14931,31 +14931,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I10" t="n">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="J10" t="n">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -14964,15 +14964,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>676254</v>
+        <v>666374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ryan Walker</t>
+          <t>Matt Brash</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14990,22 +14990,22 @@
         <v>63</v>
       </c>
       <c r="I11" t="n">
-        <v>463</v>
+        <v>388</v>
       </c>
       <c r="J11" t="n">
-        <v>463</v>
+        <v>388</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -15014,15 +15014,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTX Gambit</t>
+          <t>Logan &amp;amp</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>674003</v>
+        <v>668933</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Graham Ashcraft</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -15031,86 +15031,86 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I12" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="J12" t="n">
-        <v>252.9</v>
+        <v>378</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Logan &amp;amp</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>621237</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>José Alvarado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>64</v>
+      </c>
+      <c r="G13" t="n">
+        <v>64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>373</v>
+      </c>
+      <c r="J13" t="n">
+        <v>373</v>
+      </c>
+      <c r="K13" t="n">
         <v>3</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Logan &amp;amp</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>621242</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Edwin Díaz</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>66</v>
-      </c>
-      <c r="G13" t="n">
-        <v>66</v>
-      </c>
-      <c r="H13" t="n">
-        <v>66</v>
-      </c>
-      <c r="I13" t="n">
-        <v>534</v>
-      </c>
-      <c r="J13" t="n">
-        <v>534</v>
-      </c>
-      <c r="K13" t="n">
-        <v>36</v>
-      </c>
       <c r="L13" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -15118,11 +15118,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>547973</v>
+        <v>657649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aroldis Chapman</t>
+          <t>Jared Koenig</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -15131,31 +15131,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>499</v>
+        <v>365</v>
       </c>
       <c r="J14" t="n">
-        <v>499</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>31</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -15164,15 +15164,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>628452</v>
+        <v>661395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raisel Iglesias</t>
+          <t>Jhoan Duran</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -15181,31 +15181,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>458</v>
+        <v>563</v>
       </c>
       <c r="J15" t="n">
-        <v>458</v>
+        <v>563</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -15214,15 +15214,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>666374</v>
+        <v>691799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Matt Brash</t>
+          <t>Grant Taylor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -15231,31 +15231,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>388</v>
+        <v>540</v>
       </c>
       <c r="J16" t="n">
-        <v>388</v>
+        <v>540</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -15264,15 +15264,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>621237</v>
+        <v>662253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>José Alvarado</t>
+          <t>Andrés Muñoz</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -15290,22 +15290,22 @@
         <v>64</v>
       </c>
       <c r="I17" t="n">
-        <v>373</v>
+        <v>491</v>
       </c>
       <c r="J17" t="n">
-        <v>373</v>
+        <v>491</v>
       </c>
       <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>12</v>
-      </c>
-      <c r="N17" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -15314,15 +15314,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Logan &amp;amp</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>668933</v>
+        <v>676254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Graham Ashcraft</t>
+          <t>Ryan Walker</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -15331,48 +15331,48 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="H18" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="J18" t="n">
-        <v>168.6</v>
+        <v>463</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9</v>
+        <v>27</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Naylor? I</t>
+          <t>NTX Gambit</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>670280</v>
+        <v>674003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>David Bednar</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -15381,31 +15381,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I19" t="n">
-        <v>504</v>
+        <v>277</v>
       </c>
       <c r="J19" t="n">
-        <v>504</v>
+        <v>277</v>
       </c>
       <c r="K19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -15418,11 +15418,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>668941</v>
+        <v>670280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JoJo Romero</t>
+          <t>David Bednar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -15431,31 +15431,31 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I20" t="n">
-        <v>393</v>
+        <v>504</v>
       </c>
       <c r="J20" t="n">
-        <v>393</v>
+        <v>504</v>
       </c>
       <c r="K20" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="M20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -15468,11 +15468,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>621381</v>
+        <v>668941</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Matt Strahm</t>
+          <t>JoJo Romero</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15481,31 +15481,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H21" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I21" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J21" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -15518,11 +15518,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>666808</v>
+        <v>621381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Camilo Doval</t>
+          <t>Matt Strahm</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -15531,31 +15531,31 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I22" t="n">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="J22" t="n">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -15568,11 +15568,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>643410</v>
+        <v>666808</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mark Leiter Jr.</t>
+          <t>Camilo Doval</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15590,22 +15590,22 @@
         <v>64</v>
       </c>
       <c r="I23" t="n">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="J23" t="n">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -15618,11 +15618,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>689981</v>
+        <v>643410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>River Ryan</t>
+          <t>Mark Leiter Jr.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -15631,48 +15631,48 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="H24" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I24" t="n">
-        <v>114</v>
+        <v>347</v>
       </c>
       <c r="J24" t="n">
-        <v>90.5</v>
+        <v>347</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mirkwood S</t>
+          <t>Naylor? I</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>650556</v>
+        <v>689981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bryan Abreu</t>
+          <t>River Ryan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -15681,31 +15681,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="I25" t="n">
-        <v>426</v>
+        <v>114</v>
       </c>
       <c r="J25" t="n">
-        <v>426</v>
+        <v>114</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -15718,11 +15718,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>670970</v>
+        <v>650556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Adrian Morejon</t>
+          <t>Bryan Abreu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -15740,16 +15740,16 @@
         <v>68</v>
       </c>
       <c r="I26" t="n">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="J26" t="n">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
         <v>13</v>
@@ -15768,11 +15768,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>663158</v>
+        <v>670970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Robert Suarez</t>
+          <t>Adrian Morejon</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -15781,31 +15781,31 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I27" t="n">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="J27" t="n">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -15818,11 +15818,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>676617</v>
+        <v>663158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Riley O'Brien</t>
+          <t>Robert Suarez</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15831,31 +15831,31 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I28" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="J28" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -15868,11 +15868,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>681911</v>
+        <v>676617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Alex Vesia</t>
+          <t>Riley O'Brien</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -15881,48 +15881,48 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I29" t="n">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="J29" t="n">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Continenta</t>
+          <t>Mirkwood S</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>664126</v>
+        <v>681911</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pete Fairbanks</t>
+          <t>Alex Vesia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -15931,31 +15931,31 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I30" t="n">
-        <v>455</v>
+        <v>350</v>
       </c>
       <c r="J30" t="n">
-        <v>455</v>
+        <v>350</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -15968,11 +15968,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>678606</v>
+        <v>664126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jose A. Ferrer</t>
+          <t>Pete Fairbanks</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15981,31 +15981,31 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H31" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I31" t="n">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="J31" t="n">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="M31" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -16018,11 +16018,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>622554</v>
+        <v>678606</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Seranthony Domínguez</t>
+          <t>Jose A. Ferrer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -16031,31 +16031,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G32" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H32" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I32" t="n">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="J32" t="n">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="K32" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -16068,11 +16068,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>683769</v>
+        <v>622554</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hunter Gaddis</t>
+          <t>Seranthony Domínguez</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -16081,31 +16081,31 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G33" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H33" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I33" t="n">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="J33" t="n">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -16118,11 +16118,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>640448</v>
+        <v>683769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kyle Finnegan</t>
+          <t>Hunter Gaddis</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16131,48 +16131,48 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G34" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H34" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I34" t="n">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="J34" t="n">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hit the Kw</t>
+          <t>Continenta</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>664854</v>
+        <v>640448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ryan Helsley</t>
+          <t>Kyle Finnegan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16190,22 +16190,22 @@
         <v>64</v>
       </c>
       <c r="I35" t="n">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="J35" t="n">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="K35" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
@@ -16218,11 +16218,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>656546</v>
+        <v>664854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jeff Hoffman</t>
+          <t>Ryan Helsley</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -16231,25 +16231,25 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I36" t="n">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="J36" t="n">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M36" t="n">
         <v>4</v>
@@ -16268,11 +16268,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>642397</v>
+        <v>656546</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gregory Soto</t>
+          <t>Jeff Hoffman</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -16281,31 +16281,31 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G37" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H37" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I37" t="n">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="J37" t="n">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="K37" t="n">
+        <v>26</v>
+      </c>
+      <c r="L37" t="n">
+        <v>26</v>
+      </c>
+      <c r="M37" t="n">
         <v>4</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>4</v>
-      </c>
-      <c r="M37" t="n">
-        <v>14</v>
-      </c>
-      <c r="N37" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -16318,11 +16318,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>668674</v>
+        <v>642397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lucas Erceg</t>
+          <t>Gregory Soto</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -16331,31 +16331,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G38" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H38" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I38" t="n">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="J38" t="n">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -16368,11 +16368,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>669203</v>
+        <v>668674</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Corbin Burnes</t>
+          <t>Lucas Erceg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -16381,48 +16381,48 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G39" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H39" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="I39" t="n">
-        <v>180</v>
+        <v>332</v>
       </c>
       <c r="J39" t="n">
-        <v>180</v>
+        <v>332</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apple Cinn</t>
+          <t>Hit the Kw</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>695243</v>
+        <v>669203</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mason Miller</t>
+          <t>Corbin Burnes</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -16431,31 +16431,31 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="G40" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="H40" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="I40" t="n">
-        <v>558</v>
+        <v>180</v>
       </c>
       <c r="J40" t="n">
-        <v>558</v>
+        <v>180</v>
       </c>
       <c r="K40" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -16468,11 +16468,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>671922</v>
+        <v>695243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cade Smith</t>
+          <t>Mason Miller</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -16481,31 +16481,31 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H41" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I41" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="J41" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -16518,11 +16518,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>682842</v>
+        <v>671922</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Abner Uribe</t>
+          <t>Cade Smith</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -16531,31 +16531,31 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G42" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H42" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I42" t="n">
-        <v>478</v>
+        <v>552</v>
       </c>
       <c r="J42" t="n">
-        <v>478</v>
+        <v>552</v>
       </c>
       <c r="K42" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -16568,11 +16568,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>694037</v>
+        <v>682842</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Daniel Palencia</t>
+          <t>Abner Uribe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -16581,31 +16581,31 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G43" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H43" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I43" t="n">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="J43" t="n">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -16618,11 +16618,11 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>682254</v>
+        <v>694037</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mason Montgomery</t>
+          <t>Daniel Palencia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -16631,31 +16631,31 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I44" t="n">
-        <v>314</v>
+        <v>459</v>
       </c>
       <c r="J44" t="n">
-        <v>314</v>
+        <v>459</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="M44" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -16684,45 +16684,45 @@
         <v>64</v>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="I45" t="n">
         <v>327</v>
       </c>
       <c r="J45" t="n">
-        <v>76.59999999999999</v>
+        <v>327</v>
       </c>
       <c r="K45" t="n">
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="M45" t="n">
         <v>11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Smoking He</t>
+          <t>Apple Cinn</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>642207</v>
+        <v>682254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Devin Williams</t>
+          <t>Mason Montgomery</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -16731,48 +16731,48 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H46" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I46" t="n">
-        <v>503</v>
+        <v>314</v>
       </c>
       <c r="J46" t="n">
-        <v>503</v>
+        <v>314</v>
       </c>
       <c r="K46" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Smoking He</t>
+          <t>Apple Cinn</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>623352</v>
+        <v>801139</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Josh Hader</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -16781,31 +16781,31 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>450</v>
+        <v>194</v>
       </c>
       <c r="J47" t="n">
-        <v>450</v>
+        <v>4.2</v>
       </c>
       <c r="K47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -16818,11 +16818,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>690925</v>
+        <v>642207</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Clayton Beeter</t>
+          <t>Devin Williams</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -16831,31 +16831,31 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G48" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H48" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I48" t="n">
-        <v>380</v>
+        <v>503</v>
       </c>
       <c r="J48" t="n">
-        <v>380</v>
+        <v>503</v>
       </c>
       <c r="K48" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L48" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -16868,11 +16868,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>694335</v>
+        <v>623352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Matt Svanson</t>
+          <t>Josh Hader</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -16881,31 +16881,31 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I49" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="J49" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -16918,11 +16918,11 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>686993</v>
+        <v>690925</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Justin Sterner</t>
+          <t>Clayton Beeter</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -16931,31 +16931,31 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G50" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H50" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I50" t="n">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="J50" t="n">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="K50" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L50" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="M50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -16968,11 +16968,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>686580</v>
+        <v>694335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Justin Slaten</t>
+          <t>Matt Svanson</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -16981,48 +16981,48 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="I51" t="n">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="J51" t="n">
-        <v>166.6</v>
+        <v>360</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>Smoking He</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>643377</v>
+        <v>686993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Justin Sterner</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -17031,25 +17031,25 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G52" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H52" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I52" t="n">
-        <v>478</v>
+        <v>338</v>
       </c>
       <c r="J52" t="n">
-        <v>478</v>
+        <v>338</v>
       </c>
       <c r="K52" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L52" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M52" t="n">
         <v>10</v>
@@ -17060,19 +17060,19 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>Smoking He</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>608032</v>
+        <v>686580</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Carlos Estévez</t>
+          <t>Justin Slaten</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -17081,48 +17081,48 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G53" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H53" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I53" t="n">
-        <v>434</v>
+        <v>308</v>
       </c>
       <c r="J53" t="n">
-        <v>434</v>
+        <v>308</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>Smoking He</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>676477</v>
+        <v>678022</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Garrett Whitlock</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -17131,31 +17131,31 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="H54" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I54" t="n">
-        <v>427</v>
+        <v>178</v>
       </c>
       <c r="J54" t="n">
-        <v>427</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55">
@@ -17164,15 +17164,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>669093</v>
+        <v>686973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jeremiah Estrada</t>
+          <t>Louis Varland</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -17181,31 +17181,31 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G55" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H55" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I55" t="n">
-        <v>412</v>
+        <v>361</v>
       </c>
       <c r="J55" t="n">
-        <v>412</v>
+        <v>361</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -17214,15 +17214,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>641745</v>
+        <v>663947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Brad Keller</t>
+          <t>Tyler Holton</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -17231,31 +17231,31 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G56" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H56" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I56" t="n">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="J56" t="n">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -17264,15 +17264,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>695684</v>
+        <v>689147</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Elmer Rodríguez</t>
+          <t>Orion Kerkering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -17281,31 +17281,31 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>355</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>355</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -17314,15 +17314,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Big Lu</t>
+          <t>The Sandma</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>671212</v>
+        <v>623474</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Joe Boyle</t>
+          <t>Jimmy Herget</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -17331,36 +17331,36 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="I58" t="n">
-        <v>255</v>
+        <v>379</v>
       </c>
       <c r="J58" t="n">
-        <v>15.9</v>
+        <v>354.4</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N58" t="n">
-        <v>0.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -17368,11 +17368,11 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>686973</v>
+        <v>595345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Louis Varland</t>
+          <t>Steven Okert</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -17381,36 +17381,36 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G59" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H59" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I59" t="n">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="J59" t="n">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -17418,11 +17418,11 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>663947</v>
+        <v>621383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tyler Holton</t>
+          <t>Tanner Banks</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -17431,31 +17431,31 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G60" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H60" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I60" t="n">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="J60" t="n">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
@@ -17464,15 +17464,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>689147</v>
+        <v>643377</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Orion Kerkering</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -17481,31 +17481,31 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G61" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H61" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I61" t="n">
-        <v>355</v>
+        <v>478</v>
       </c>
       <c r="J61" t="n">
-        <v>355</v>
+        <v>478</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M61" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -17514,15 +17514,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>595345</v>
+        <v>608032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Steven Okert</t>
+          <t>Carlos Estévez</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -17531,31 +17531,31 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G62" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H62" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I62" t="n">
-        <v>334</v>
+        <v>434</v>
       </c>
       <c r="J62" t="n">
-        <v>334</v>
+        <v>434</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M62" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -17564,15 +17564,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>621383</v>
+        <v>676477</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tanner Banks</t>
+          <t>Garrett Whitlock</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -17581,31 +17581,31 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G63" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H63" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I63" t="n">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="J63" t="n">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
@@ -17614,15 +17614,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Sandma</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>623474</v>
+        <v>669093</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jimmy Herget</t>
+          <t>Jeremiah Estrada</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -17631,48 +17631,48 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G64" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="H64" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="I64" t="n">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="J64" t="n">
-        <v>108.3</v>
+        <v>412</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>15</v>
       </c>
       <c r="N64" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H-Town Ram</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>656730</v>
+        <v>641745</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Trevor Megill</t>
+          <t>Brad Keller</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -17681,48 +17681,48 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G65" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H65" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I65" t="n">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="J65" t="n">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="K65" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N65" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H-Town Ram</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>664076</v>
+        <v>671212</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Garrett Cleavinger</t>
+          <t>Joe Boyle</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -17731,48 +17731,48 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G66" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H66" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I66" t="n">
-        <v>394</v>
+        <v>255</v>
       </c>
       <c r="J66" t="n">
-        <v>394</v>
+        <v>215.2</v>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>13</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H-Town Ram</t>
+          <t>The Big Lu</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>656945</v>
+        <v>695684</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tanner Scott</t>
+          <t>Elmer Rodríguez</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -17781,31 +17781,31 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>379</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>379</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -17818,43 +17818,193 @@
         </is>
       </c>
       <c r="C68" t="n">
+        <v>656730</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Trevor Megill</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>66</v>
+      </c>
+      <c r="G68" t="n">
+        <v>66</v>
+      </c>
+      <c r="H68" t="n">
+        <v>66</v>
+      </c>
+      <c r="I68" t="n">
+        <v>422</v>
+      </c>
+      <c r="J68" t="n">
+        <v>422</v>
+      </c>
+      <c r="K68" t="n">
+        <v>11</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11</v>
+      </c>
+      <c r="M68" t="n">
+        <v>9</v>
+      </c>
+      <c r="N68" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>H-Town Ram</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>664076</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Garrett Cleavinger</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>66</v>
+      </c>
+      <c r="G69" t="n">
+        <v>66</v>
+      </c>
+      <c r="H69" t="n">
+        <v>66</v>
+      </c>
+      <c r="I69" t="n">
+        <v>394</v>
+      </c>
+      <c r="J69" t="n">
+        <v>394</v>
+      </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" t="n">
+        <v>8</v>
+      </c>
+      <c r="M69" t="n">
+        <v>13</v>
+      </c>
+      <c r="N69" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>12</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>H-Town Ram</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>656945</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tanner Scott</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>63</v>
+      </c>
+      <c r="G70" t="n">
+        <v>63</v>
+      </c>
+      <c r="H70" t="n">
+        <v>63</v>
+      </c>
+      <c r="I70" t="n">
+        <v>379</v>
+      </c>
+      <c r="J70" t="n">
+        <v>379</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" t="n">
+        <v>15</v>
+      </c>
+      <c r="N70" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>12</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>H-Town Ram</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
         <v>664208</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Phil Maton</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F71" t="n">
         <v>65</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G71" t="n">
         <v>65</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H71" t="n">
         <v>65</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I71" t="n">
         <v>342</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J71" t="n">
         <v>342</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K71" t="n">
         <v>4</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M71" t="n">
         <v>14</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N71" t="n">
         <v>14</v>
       </c>
     </row>
@@ -18830,10 +18980,10 @@
         <v>801139</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="27">
@@ -19192,10 +19342,10 @@
         <v>673929</v>
       </c>
       <c r="H36" t="n">
-        <v>76.59999999999999</v>
+        <v>327</v>
       </c>
       <c r="I36" t="n">
-        <v>38.3</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="37">
@@ -22181,10 +22331,10 @@
         <v>596133</v>
       </c>
       <c r="H117" t="n">
-        <v>158.5</v>
+        <v>354</v>
       </c>
       <c r="I117" t="n">
-        <v>158.5</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118">
@@ -25939,10 +26089,10 @@
         <v>668933</v>
       </c>
       <c r="H219" t="n">
-        <v>168.6</v>
+        <v>378</v>
       </c>
       <c r="I219" t="n">
-        <v>56.2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="220">
@@ -26013,10 +26163,10 @@
         <v>657649</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="222">
@@ -28961,10 +29111,10 @@
         <v>674003</v>
       </c>
       <c r="H301" t="n">
-        <v>252.9</v>
+        <v>277</v>
       </c>
       <c r="I301" t="n">
-        <v>252.9</v>
+        <v>277</v>
       </c>
     </row>
     <row r="302">
@@ -29849,10 +29999,10 @@
         <v>689981</v>
       </c>
       <c r="H325" t="n">
-        <v>90.5</v>
+        <v>114</v>
       </c>
       <c r="I325" t="n">
-        <v>22.62</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="326">
@@ -31284,10 +31434,10 @@
         <v>678022</v>
       </c>
       <c r="H364" t="n">
-        <v>0</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I364" t="n">
-        <v>0</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="365">
@@ -31506,10 +31656,10 @@
         <v>686580</v>
       </c>
       <c r="H370" t="n">
-        <v>166.6</v>
+        <v>308</v>
       </c>
       <c r="I370" t="n">
-        <v>55.53</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="371">
@@ -32686,10 +32836,10 @@
         <v>671212</v>
       </c>
       <c r="H402" t="n">
-        <v>15.9</v>
+        <v>215.2</v>
       </c>
       <c r="I402" t="n">
-        <v>5.3</v>
+        <v>71.73</v>
       </c>
     </row>
     <row r="403">
@@ -34339,10 +34489,10 @@
         <v>623474</v>
       </c>
       <c r="H447" t="n">
-        <v>108.3</v>
+        <v>354.4</v>
       </c>
       <c r="I447" t="n">
-        <v>108.3</v>
+        <v>354.4</v>
       </c>
     </row>
     <row r="448">

--- a/ottoneu_power_rankings.xlsx
+++ b/ottoneu_power_rankings.xlsx
@@ -655,13 +655,13 @@
         <v>44.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1771.8</v>
+        <v>1531.2</v>
       </c>
       <c r="T2" t="n">
-        <v>572.7</v>
+        <v>494.9</v>
       </c>
       <c r="U2" t="n">
-        <v>207.1</v>
+        <v>179</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -764,13 +764,13 @@
         <v>57.8</v>
       </c>
       <c r="S3" t="n">
-        <v>1831</v>
+        <v>1582.4</v>
       </c>
       <c r="T3" t="n">
-        <v>541.9</v>
+        <v>468.3</v>
       </c>
       <c r="U3" t="n">
-        <v>192.3</v>
+        <v>166.2</v>
       </c>
       <c r="V3" t="n">
         <v>3.51</v>
@@ -873,13 +873,13 @@
         <v>23.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1813.4</v>
+        <v>1567.2</v>
       </c>
       <c r="T4" t="n">
-        <v>501.1</v>
+        <v>433</v>
       </c>
       <c r="U4" t="n">
-        <v>187.8</v>
+        <v>162.3</v>
       </c>
       <c r="V4" t="n">
         <v>3.43</v>
@@ -982,13 +982,13 @@
         <v>48.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1819.1</v>
+        <v>1572</v>
       </c>
       <c r="T5" t="n">
-        <v>564.1</v>
+        <v>487.5</v>
       </c>
       <c r="U5" t="n">
-        <v>199.2</v>
+        <v>172.2</v>
       </c>
       <c r="V5" t="n">
         <v>3.64</v>
@@ -1091,13 +1091,13 @@
         <v>55.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1798.5</v>
+        <v>1554.3</v>
       </c>
       <c r="T6" t="n">
-        <v>567.5</v>
+        <v>490.4</v>
       </c>
       <c r="U6" t="n">
-        <v>218</v>
+        <v>188.4</v>
       </c>
       <c r="V6" t="n">
         <v>3.79</v>
@@ -1200,13 +1200,13 @@
         <v>30.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1730</v>
+        <v>1495.1</v>
       </c>
       <c r="T7" t="n">
-        <v>569.7</v>
+        <v>492.3</v>
       </c>
       <c r="U7" t="n">
-        <v>196.8</v>
+        <v>170.1</v>
       </c>
       <c r="V7" t="n">
         <v>3.73</v>
@@ -1309,13 +1309,13 @@
         <v>45.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1681.6</v>
+        <v>1453.2</v>
       </c>
       <c r="T8" t="n">
-        <v>533.5</v>
+        <v>461.1</v>
       </c>
       <c r="U8" t="n">
-        <v>195.8</v>
+        <v>169.2</v>
       </c>
       <c r="V8" t="n">
         <v>3.74</v>
@@ -1418,13 +1418,13 @@
         <v>47.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1708.1</v>
+        <v>1476.2</v>
       </c>
       <c r="T9" t="n">
-        <v>586</v>
+        <v>506.5</v>
       </c>
       <c r="U9" t="n">
-        <v>203.5</v>
+        <v>175.9</v>
       </c>
       <c r="V9" t="n">
         <v>3.91</v>
@@ -1527,13 +1527,13 @@
         <v>34.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1675.6</v>
+        <v>1448</v>
       </c>
       <c r="T10" t="n">
-        <v>606.4</v>
+        <v>524</v>
       </c>
       <c r="U10" t="n">
-        <v>179.2</v>
+        <v>154.8</v>
       </c>
       <c r="V10" t="n">
         <v>3.77</v>
@@ -1636,13 +1636,13 @@
         <v>44.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1566</v>
+        <v>1353.3</v>
       </c>
       <c r="T11" t="n">
-        <v>501</v>
+        <v>433</v>
       </c>
       <c r="U11" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="V11" t="n">
         <v>3.77</v>
@@ -1745,13 +1745,13 @@
         <v>71.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1351.6</v>
+        <v>1168</v>
       </c>
       <c r="T12" t="n">
-        <v>467.1</v>
+        <v>403.7</v>
       </c>
       <c r="U12" t="n">
-        <v>176.6</v>
+        <v>152.6</v>
       </c>
       <c r="V12" t="n">
         <v>3.93</v>
@@ -1854,13 +1854,13 @@
         <v>51.6</v>
       </c>
       <c r="S13" t="n">
-        <v>1625</v>
+        <v>1404.3</v>
       </c>
       <c r="T13" t="n">
-        <v>566.4</v>
+        <v>489.4</v>
       </c>
       <c r="U13" t="n">
-        <v>179.1</v>
+        <v>154.8</v>
       </c>
       <c r="V13" t="n">
         <v>3.78</v>
